--- a/output/graficos_educacion_tasas/comunal_e_mat_a_2024_tarapaca.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_mat_a_2024_tarapaca.xlsx
@@ -54,7 +54,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 17:50</t>
+    <t xml:space="preserve">2026-09-09 20:57</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_mat_a_2024_tarapaca.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_mat_a_2024_tarapaca.xlsx
@@ -24,27 +24,27 @@
     <t xml:space="preserve">Valor (%)</t>
   </si>
   <si>
+    <t xml:space="preserve">Iquique</t>
+  </si>
+  <si>
     <t xml:space="preserve">Alto Hospicio</t>
   </si>
   <si>
+    <t xml:space="preserve">Pozo Almonte</t>
+  </si>
+  <si>
     <t xml:space="preserve">Camiña</t>
   </si>
   <si>
+    <t xml:space="preserve">Huara</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pica</t>
+  </si>
+  <si>
     <t xml:space="preserve">Colchane</t>
   </si>
   <si>
-    <t xml:space="preserve">Huara</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Iquique</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pica</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pozo Almonte</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -54,7 +54,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:57</t>
+    <t xml:space="preserve">2026-09-18 10:47</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -466,7 +466,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>73.03</v>
+        <v>73.36</v>
       </c>
     </row>
     <row r="3">
@@ -474,7 +474,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>73.21</v>
+        <v>73.03</v>
       </c>
     </row>
     <row r="4">
@@ -482,7 +482,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>62.84</v>
+        <v>71.54</v>
       </c>
     </row>
     <row r="5">
@@ -490,7 +490,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>72.86</v>
+        <v>73.21</v>
       </c>
     </row>
     <row r="6">
@@ -498,7 +498,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>73.36</v>
+        <v>72.86</v>
       </c>
     </row>
     <row r="7">
@@ -514,7 +514,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>71.54</v>
+        <v>62.84</v>
       </c>
     </row>
   </sheetData>
